--- a/static/standards-correlations/Ohio_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Ohio_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$56</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Ohio CS Standards adopted July 2022 | Advanced level NOT included</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Ohio CS Standards adopted July 2022 | Advanced level NOT included</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1080,7 +1081,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers the social risk (phishing) and Ext 5.3G (Secret Messages / HTTPS) the digital one. Physical risk, quantum key distribution, and cluster computing are absent.</t>
+          <t>Introductory Systems 10 covers the social risk (phishing) and Ext 5.3G (Secret Messages / HTTPS) the digital one. Physical risk, quantum key distribution, and cluster computing are absent.</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1233,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Ext 4.2E (A Basic Building Block of AI) names transport and aviation applications and Discovery Coding 2 covers professional practice. Career pathway planning is not a curriculum activity.</t>
+          <t>Ext 4.2E (A Basic Building Block of AI) names transport and aviation applications and Introductory Coding 2 covers professional practice. Career pathway planning is not a curriculum activity.</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1444,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Ohio names visual artifacts. Discovery Systems 4 teaches flowcharting and Ext 1.2B (Dependency Map) produces a node-and-arrow structure diagram, both applied to a real scored problem.</t>
+          <t>Ohio names visual artifacts. Introductory Systems 4 teaches flowcharting and Ext 1.2B (Dependency Map) produces a node-and-arrow structure diagram, both applied to a real scored problem.</t>
         </is>
       </c>
     </row>
@@ -2690,6 +2691,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -2734,7 +2736,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2748,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2858,6 +2860,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
@@ -2879,7 +2883,7 @@
 SOURCE NOTE: Codes and statements transcribed from the CodeHS published Ohio 9-12 Foundational framework. The July 2022 adoption and the Foundational/Advanced split were verified against Ohio Department of Education. Verify wording against the official OCS_Adopted-2022 document before any formal submission.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
